--- a/dataset/lecture_5_output/NPASS_NPT204_RDKit_activity_output_DNN.xlsx
+++ b/dataset/lecture_5_output/NPASS_NPT204_RDKit_activity_output_DNN.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,74 +429,74 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Random Seed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Internal ACC</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Internal AUC</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>External ACC</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>External AUC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>External Sensitivity</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>External Specificity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>External BA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>2023</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9196428656578064</v>
+        <v>0.9491525292396545</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9802296161651611</v>
+        <v>0.9933208823204041</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7037037037037037</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="F2" t="n">
-        <v>0.693415641784668</v>
+        <v>0.6893004179000854</v>
       </c>
       <c r="G2" t="n">
         <v>0.75</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.7416666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/lecture_5_output/NPASS_NPT204_RDKit_activity_output_DNN.xlsx
+++ b/dataset/lecture_5_output/NPASS_NPT204_RDKit_activity_output_DNN.xlsx
@@ -425,78 +425,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Random Seed</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Random Seed</t>
+          <t>Threshold</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Internal ACC</t>
+          <t>Best Epoch</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Internal AUC</t>
+          <t>Best Val Loss</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>External ACC</t>
+          <t>Train ACC</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>External AUC</t>
+          <t>Train AUC</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>External Sensitivity</t>
+          <t>Train PRAUC</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>External Specificity</t>
+          <t>Test ACC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>External BA</t>
+          <t>Test Precision</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Test AUC</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Test PRAUC</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Test Sensitivity</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Test Specificity</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Test Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Test F1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Test MCC</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
+      <c r="A2" t="n">
+        <v>2023</v>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9491525292396545</v>
+        <v>109</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9933208823204041</v>
+        <v>0.6894148588180542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7711864406779662</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6893004179000854</v>
+        <v>0.8394139615053146</v>
       </c>
       <c r="G2" t="n">
-        <v>0.75</v>
+        <v>0.8415058574820959</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4944444444444445</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5044391123009544</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2857142857142858</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.158113883008419</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/lecture_5_output/NPASS_NPT204_RDKit_activity_output_DNN.xlsx
+++ b/dataset/lecture_5_output/NPASS_NPT204_RDKit_activity_output_DNN.xlsx
@@ -538,58 +538,58 @@
         <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6894148588180542</v>
+        <v>178186528</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7711864406779662</v>
+        <v>0.5943396226415094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8394139615053146</v>
+        <v>0.7677605481428056</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8415058574820959</v>
+        <v>0.7124159424846265</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4944444444444445</v>
+        <v>0.4777777777777777</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5044391123009544</v>
+        <v>0.5484430933280038</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.425</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.158113883008419</v>
+        <v>0.2192645048267573</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
